--- a/result.xlsx
+++ b/result.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -626,7 +626,7 @@
         <v>42.77359999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>793.5507200000001</v>
+        <v>991.9384000000001</v>
       </c>
       <c r="F9" t="n">
         <v>97.05593636363636</v>
@@ -752,8 +752,33 @@
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="n">
-        <v>934.0483629629629</v>
-      </c>
+        <v>969.9732999999999</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ZP</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Без продукта</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>267.9206409090909</v>
+      </c>
+      <c r="D16" t="n">
+        <v>769.6465111111111</v>
+      </c>
+      <c r="E16" t="n">
+        <v>3088.643814285715</v>
+      </c>
+      <c r="F16" t="n">
+        <v>911.2207749999999</v>
+      </c>
+      <c r="G16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
